--- a/docs/sprint3/execution-log.xlsx
+++ b/docs/sprint3/execution-log.xlsx
@@ -443,17 +443,18 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H20"/>
+  <dimension ref="A1:I21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
     <col width="9" customWidth="1" min="2" max="2"/>
     <col width="11" customWidth="1" min="3" max="3"/>
-    <col width="11" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
     <col width="24" customWidth="1" min="5" max="5"/>
-    <col width="9" customWidth="1" min="6" max="6"/>
-    <col width="10" customWidth="1" min="7" max="7"/>
-    <col width="48" customWidth="1" min="8" max="8"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="9" customWidth="1" min="7" max="7"/>
+    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="46" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
@@ -484,17 +485,22 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
+          <t>Крок</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
           <t>Статус</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Bug ID</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>Коментар</t>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Коментар (фактичний результат)</t>
         </is>
       </c>
     </row>
@@ -521,18 +527,19 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>demo 21.10.2026, Chrome / Win11</t>
-        </is>
-      </c>
-      <c r="F2" s="2" t="inlineStr">
+          <t>demo 21.10.2026, Chrome 129.0 / Windows 11</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr"/>
+      <c r="G2" s="2" t="inlineStr">
         <is>
           <t>passed</t>
         </is>
       </c>
-      <c r="G2" s="2" t="inlineStr"/>
-      <c r="H2" s="2" t="inlineStr">
-        <is>
-          <t>Вхід працює; відкрито Dashboard з меню модулів (підтверджено вживу)</t>
+      <c r="H2" s="2" t="inlineStr"/>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>Вхід працює; відкрито Dashboard з бічним меню модулів</t>
         </is>
       </c>
     </row>
@@ -559,22 +566,27 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>demo 21.10.2026, Chrome / Win11</t>
+          <t>demo 21.10.2026, Chrome 129.0 / Windows 11</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
+          <t>крок 4</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
           <t>failed</t>
         </is>
       </c>
-      <c r="G3" s="2" t="inlineStr">
+      <c r="H3" s="2" t="inlineStr">
         <is>
           <t>BUG-002</t>
         </is>
       </c>
-      <c r="H3" s="2" t="inlineStr">
-        <is>
-          <t>Показано «Invalid credentials» замість «Wrong username or password» (підтверджено, скрін)</t>
+      <c r="I3" s="2" t="inlineStr">
+        <is>
+          <t>Показано «Invalid credentials» замість «Wrong username or password» (GUI-20)</t>
         </is>
       </c>
     </row>
@@ -601,18 +613,19 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>demo 21.10.2026, Chrome / Win11</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
+          <t>demo 21.10.2026, Chrome 129.0 / Windows 11</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr"/>
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>passed</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr"/>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>Порожні поля → «Required» (поведінка GUI-40)</t>
+      <c r="H4" s="2" t="inlineStr"/>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>Порожні поля → «Required» під кожним; запит не надіслано</t>
         </is>
       </c>
     </row>
@@ -639,18 +652,19 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>demo 21.10.2026, Chrome / Win11</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
+          <t>demo 21.10.2026, Chrome 129.0 / Windows 11</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr"/>
+      <c r="G5" s="2" t="inlineStr">
         <is>
           <t>passed</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr"/>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>Користувача зі стійким паролем збережено</t>
+      <c r="H5" s="2" t="inlineStr"/>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>Користувача teame.user04 зі стійким паролем збережено («Successfully Saved»)</t>
         </is>
       </c>
     </row>
@@ -677,22 +691,27 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>demo 21.10.2026, Chrome / Win11</t>
+          <t>demo 21.10.2026, Chrome 129.0 / Windows 11</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
+          <t>крок 3 (рядки 2,3)</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
           <t>failed</t>
         </is>
       </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>BUG-001</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>Пароль «Testuser1» без спецсимволу збережено (лише позначка Weak) — підтверджено, скрін</t>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>Паролі «Teampass1» (без спецсимволу) і «teampass1!» (без великої) збережено — лише позначка Weak</t>
         </is>
       </c>
     </row>
@@ -719,18 +738,19 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>demo 21.10.2026, Chrome / Win11</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
+          <t>demo 21.10.2026, Chrome 129.0 / Windows 11</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr"/>
+      <c r="G7" s="2" t="inlineStr">
         <is>
           <t>passed</t>
         </is>
       </c>
-      <c r="G7" s="2" t="inlineStr"/>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>Колонки й фільтри відповідають F-40/GUI-60 (підтверджено вживу)</t>
+      <c r="H7" s="2" t="inlineStr"/>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>«(N) Records Found» показано; фільтр Amelia і сортування працюють; колонки за F-40</t>
         </is>
       </c>
     </row>
@@ -757,22 +777,27 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>demo 21.10.2026, Chrome / Win11</t>
+          <t>demo 21.10.2026, Chrome 129.0 / Windows 11</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
+          <t>крок 5</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>failed</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>BUG-003</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>Поле РНОКПП на формі Add Employee відсутнє — підтверджено, скрін</t>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>Поле РНОКПП на формі Add Employee і в профілі відсутнє — валідацію F-50 виконати неможливо</t>
         </is>
       </c>
     </row>
@@ -799,20 +824,25 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>demo 21.10.2026, Chrome / Win11</t>
+          <t>demo 21.10.2026, Chrome 129.0 / Windows 11</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
+          <t>крок 3</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
           <t>blocked</t>
         </is>
       </c>
-      <c r="G9" s="2" t="inlineStr">
+      <c r="H9" s="2" t="inlineStr">
         <is>
           <t>BUG-003</t>
         </is>
       </c>
-      <c r="H9" s="2" t="inlineStr">
+      <c r="I9" s="2" t="inlineStr">
         <is>
           <t>Заблоковано: поле РНОКПП відсутнє (див. BUG-003)</t>
         </is>
@@ -841,18 +871,19 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>demo 21.10.2026, Chrome / Win11</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
+          <t>demo 21.10.2026, Chrome 129.0 / Windows 11</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr"/>
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>passed</t>
         </is>
       </c>
-      <c r="G10" s="2" t="inlineStr"/>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>Вкладки профілю наявні; My Info — лише контактні дані</t>
+      <c r="H10" s="2" t="inlineStr"/>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>Вкладки профілю наявні; My Info редагує лише контактні дані</t>
         </is>
       </c>
     </row>
@@ -879,18 +910,19 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>demo 21.10.2026, Chrome / Win11</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>blocked</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr"/>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>Обліковий запис без ліміту: «No Leave Types with Leave Balance» — потрібен entitlement</t>
+          <t>demo 21.10.2026, Chrome 129.0 / Windows 11</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr"/>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr"/>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>Після ліміту (TC-015) баланс «10.00 Day(s)»; тривалість 19–23.10 = 5 робочих днів; заявка Pending</t>
         </is>
       </c>
     </row>
@@ -917,18 +949,19 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>demo 21.10.2026, Chrome / Win11</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
+          <t>demo 21.10.2026, Chrome 129.0 / Windows 11</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr"/>
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>passed</t>
         </is>
       </c>
-      <c r="G12" s="2" t="inlineStr"/>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>To&lt;From → «To date should be after from date» (підтверджено вживу)</t>
+      <c r="H12" s="2" t="inlineStr"/>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>3: «To date should be after from date»; 4: «Balance not sufficient» — обидві заявки не збережено</t>
         </is>
       </c>
     </row>
@@ -955,18 +988,19 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>demo 21.10.2026, Chrome / Win11</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
+          <t>demo 21.10.2026, Chrome 129.0 / Windows 11</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr"/>
+      <c r="G13" s="2" t="inlineStr">
         <is>
           <t>passed</t>
         </is>
       </c>
-      <c r="G13" s="2" t="inlineStr"/>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>Тривалість за робочими днями (BL-30) — перевірити з доданим лімітом</t>
+      <c r="H13" s="2" t="inlineStr"/>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>(1) 5, (2) 1, (3) 2 — відповідає BL-30 (сб-нд не враховано)</t>
         </is>
       </c>
     </row>
@@ -993,18 +1027,19 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>demo 21.10.2026, Chrome / Win11</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
+          <t>demo 21.10.2026, Chrome 129.0 / Windows 11</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr"/>
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>passed</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr"/>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>Перегляд і скасування Pending-заявки</t>
+      <c r="H14" s="2" t="inlineStr"/>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>Заявку створено через Apply (Pending) і скасовано у My Leave → Cancelled</t>
         </is>
       </c>
     </row>
@@ -1031,22 +1066,27 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>demo 21.10.2026, Chrome / Win11</t>
+          <t>demo 21.10.2026, Chrome 129.0 / Windows 11</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
+          <t>крок 7</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
           <t>failed</t>
         </is>
       </c>
-      <c r="G15" s="2" t="inlineStr">
+      <c r="H15" s="2" t="inlineStr">
         <is>
           <t>BUG-005</t>
         </is>
       </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>Approve/Reject працюють, нагадування про Pending &gt;24 год немає (Dashboard→My Actions) — скрін</t>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>Approve→Scheduled, Reject→Rejected працюють; нагадування про Pending &gt;24 год відсутнє (Dashboard→My Actions)</t>
         </is>
       </c>
     </row>
@@ -1073,18 +1113,19 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>demo 21.10.2026, Chrome / Win11</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
+          <t>demo 21.10.2026, Chrome 129.0 / Windows 11</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr"/>
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>passed</t>
         </is>
       </c>
-      <c r="G16" s="2" t="inlineStr"/>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>Баланс рахується; Pending не віднімається двічі (з доданим лімітом)</t>
+      <c r="H16" s="2" t="inlineStr"/>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>Ліміт 10 днів додано; призначення → Scheduled; Pending не віднімається двічі</t>
         </is>
       </c>
     </row>
@@ -1111,18 +1152,19 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>demo 21.10.2026, Chrome / Win11</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
+          <t>demo 21.10.2026, Chrome 129.0 / Windows 11</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr"/>
+      <c r="G17" s="2" t="inlineStr">
         <is>
           <t>passed</t>
         </is>
       </c>
-      <c r="G17" s="2" t="inlineStr"/>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>Після Rejected той самий табель редагується і подається повторно</t>
+      <c r="H17" s="2" t="inlineStr"/>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>Save→Not Submitted→Submit→Submitted; після Reject той самий табель відредаговано і подано повторно</t>
         </is>
       </c>
     </row>
@@ -1149,22 +1191,27 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>demo 21.10.2026, Chrome / Win11</t>
+          <t>demo 21.10.2026, Chrome 129.0 / Windows 11</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
+          <t>крок 5</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
           <t>failed</t>
         </is>
       </c>
-      <c r="G18" s="2" t="inlineStr">
+      <c r="H18" s="2" t="inlineStr">
         <is>
           <t>BUG-006</t>
         </is>
       </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>Вакансія публікується на публічній сторінці jobs.html + RSS (без входу) — підтверджено, скрін</t>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>Вакансію створено, але вона публікується на публічній сторінці jobs.html + RSS (без входу), а не лише внутрішньо</t>
         </is>
       </c>
     </row>
@@ -1191,18 +1238,19 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>demo 21.10.2026, Chrome / Win11</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
+          <t>demo 21.10.2026, Chrome 129.0 / Windows 11</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr"/>
+      <c r="G19" s="2" t="inlineStr">
         <is>
           <t>passed</t>
         </is>
       </c>
-      <c r="G19" s="2" t="inlineStr"/>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>Некоректний email відхилено: «Expected format: admin@example.com» (підтверджено вживу)</t>
+      <c r="H19" s="2" t="inlineStr"/>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>Коректний email збережено; некоректний «test18@mail» відхилено («Expected format: admin@example.com»)</t>
         </is>
       </c>
     </row>
@@ -1229,22 +1277,66 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>demo 21.10.2026, Chrome / Win11</t>
+          <t>demo 21.10.2026, Chrome 129.0 / Windows 11</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
+          <t>крок 4</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
           <t>failed</t>
         </is>
       </c>
-      <c r="G20" s="2" t="inlineStr">
+      <c r="H20" s="2" t="inlineStr">
         <is>
           <t>BUG-004</t>
         </is>
       </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>Partial Days «Specify Time» дає гранулярність у годинах, дрібнішу за 0,5 дня</t>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>Duration «Specify Time» відкриває поля часу (From/To, 09:00–11:00) — гранулярність дрібніша за крок 0,5 дня</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>Run 1</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>TC-020</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>21.10.2026</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>Аліна</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>demo 21.10.2026, Chrome 129.0 / Windows 11</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr"/>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr"/>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>Бічне меню містить усі модулі; пошук фільтрує до Leave; меню користувача — About/Support/Change Password/Logout</t>
         </is>
       </c>
     </row>
@@ -1322,7 +1414,7 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>Google Chrome (основний); Firefox — вибіркова перевірка (конфігураційне)</t>
+          <t>Google Chrome 129.0 (основний); Firefox 130 — вибіркова перевірка (конфігураційне)</t>
         </is>
       </c>
     </row>
@@ -1334,7 +1426,7 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>Windows 11</t>
+          <t>Windows 11 (23H2)</t>
         </is>
       </c>
     </row>
@@ -1370,7 +1462,7 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>BUG-001, BUG-002, BUG-003, BUG-005, BUG-006 (attachments/)</t>
+          <t>BUG-001…BUG-006 (тека attachments/)</t>
         </is>
       </c>
     </row>
@@ -1382,7 +1474,7 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>Кейси з відпустками (TC-010, TC-012, TC-015) потребують доданого ліміту (entitlement) для повного прогону; BUG-004 — зняти скрін Partial Days при такому прогоні.</t>
+          <t>Передумова для кейсів з відпустками — доданий ліміт (Leave → Entitlements), див. TC-015; лише вигадані дані, без реальних персональних.</t>
         </is>
       </c>
     </row>
